--- a/_FACTORY/_LIGNES/_TEMPLATE/A2_APPRO/A2_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/A2_APPRO/A2_THEME.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Base Items Brute.</t>
+          <t>Réservoir de matière culturelle exploitable.</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1094,10 +1094,14 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr"/>
+          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1182,26 +1186,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>

--- a/_FACTORY/_LIGNES/_TEMPLATE/A2_APPRO/A2_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/A2_APPRO/A2_THEME.xlsx
@@ -10,8 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIB_SECTIONS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIB_ITEMS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STATS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESQUISSE_POOLS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSAIRE" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,420 +791,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ESQUISSE POOLS — À partir de la structure BIB</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SECTION_BIB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NB_ITEMS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>POOL_POTENTIEL</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FORCE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CANDIDAT_AGRÉGÉ</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FUSIONNER_AVEC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>POOL_PROVISOIRE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>[Nom section]</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>QV / IF-SF / IF-ROT</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>FORT / MOYEN / FAIBLE</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>OUI / NON</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>QV-XX</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>[Section faible &lt;5 items]</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>QV</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>FAIBLE</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>[Section compatible]</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>QV-XX</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Fusion nécessaire</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>RÈGLE : si NB_ITEMS &lt; seuil pool seul → CANDIDAT_AGRÉGÉ = OUI → identifier FUSIONNER_AVEC avant A3</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>GLOSSAIRE — ÉTAPE A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Source : glossaire_documentaire_factory.md — LECTURE SEULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>TERME</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>DÉFINITION COURTE</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>RÈGLE PRINCIPALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>BIB</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Réservoir de matière culturelle exploitable.</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-BIB-001] Le BIB original ne doit jamais être modifié après archivage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSIBILITE_GRAND_PUBLIC</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Capacité d'une référence à être reconnue rapidement par le public cible.</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-AGP-001] Les pools structurants doivent privilégier une forte accessibilité.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>COBAYE</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Thème pilote utilisé pour construire ou valider un workflow avant généralisation.</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>FACTORY_PIPELINE</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Chaîne officielle de traitement documentaire.</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-PIPE-001] Aucune étape ne peut être sautée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>NAMING_PATTERN_ARTIFACT</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Fichier pouvant exister en plusieurs exemplaires ou versions dans une même phase.</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>NAMING_PATTERN_PROCESS_DOC</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Document unique produit à une phase donnée, non réitérable.</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>SESSION_RESUMPTION_PROMPT</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Document .md auto-généré par Claude quand nouvelle session s'impose (token saturation, context complexity, time checkpoi</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-SRP-001] SESSION_RESUMPTION_PROMPT généré PROACTIVE (avant rupture, pas après).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>STATUS_STANDARD</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Liste officielle des statuts documentaires autorisés.</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-STATUS-001] Tout autre format de statut est interdit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>DEPENDENCY</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Liste explicite des documents nécessaires à l'interprétation correcte d'un document.</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-DEP-001] Les références implicites sont interdites.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>MACHINE_READABLE</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Bloc structuré destiné à être interprété directement par une IA.</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>[RULE-MACHINE-001] Les données structurelles critiques doivent exister en version MACHINE_READABLE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>⚠ ALERTES — TERMES POTENTIELLEMENT MANQUANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>L'IA consigne ici tout terme utilisé dans cette étape mais absent du glossaire source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>